--- a/data/配置表/03_物品与掉落.xlsx
+++ b/data/配置表/03_物品与掉落.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>使用效果JSON（空=不可直接使用），如 {"san_restore":10} [json]</t>
+          <t>使用效果JSON，空=不可直接使用 [json]。可用键：san_restore(数值) / learn_skill(技能id 或 random) / clear_neg_trait(数值) / trigger_event(事件id，字符串) / unlock_blueprint(数组，元素为 {target_id:字符串, level:数值})</t>
         </is>
       </c>
     </row>
